--- a/InputData/indst/_cement/CSCC/Cement Calcined Clay Capital Inputs.xlsx
+++ b/InputData/indst/_cement/CSCC/Cement Calcined Clay Capital Inputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CSCC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\cement-substitute-material-cost\InputData\indst\_cement\CSCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76790FCC-6F6A-43FF-9B93-0D7721C3C40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51AF8312-8E3D-4257-BADD-B30A30C493FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>CSCC Cement Calcined Clay Capital Inputs</t>
   </si>
@@ -126,19 +126,19 @@
     <t>Purpose and layout</t>
   </si>
   <si>
-    <t>CSCC holds two numbers for the capital needed to make calcined clay, the main new ingredient of blended cements such as limestone calcined clay cement (LC3): the capital cost of a calcined clay plant per tonne of annual capacity, and the share of the material that replaces clinker that is calcined clay. When a policy (the cement measures lever, the carbon-intensity standard or low-carbon procurement) raises clinker substitution, the model builds the calcined clay capacity the extra substitution needs and adds its cost to industry 239's capital spending. Edit the 'Assumptions' tab; the 'Derivation' tab converts the capital cost to 2012 dollars; the 'CSCC' tab is exported to CSCC.csv.</t>
+    <t>CSCC holds the capital cost of a calcined clay plant per tonne of annual capacity. Calcined clay is the main new ingredient of blended cements such as limestone calcined clay cement (LC3). When a policy (the cement measures lever, the carbon-intensity standard or low-carbon procurement) raises clinker substitution, the model builds the calcined clay capacity the extra substitution needs (using the calcined clay share in the CSMI file) and adds its cost to industry 239's capital spending. Edit the 'Assumptions' tab; the 'Derivation' tab converts the capital cost to 2012 dollars; the 'CSCC' tab is exported to CSCC.csv.</t>
   </si>
   <si>
     <t>U.S. values</t>
   </si>
   <si>
-    <t>About $150 per tonne of annual calcined-clay capacity in 2024 dollars ($110 in 2012 dollars), covering the calciner, dryer, cooler and storage but not extra cement grinding: the middle of plants built or announced since 2020 ($100-290 per tonne; the 14 disclosed projects average about $123). No U.S. plant cost has been published, so the range is wide: use about $90 for a retrofit at an integrated plant and about $300 for a small or greenfield plant. The calcined clay share is 0.5, the same marginal substitution mix as the SCM production energy input (SCMEI): half calcined clay, the rest limestone, fly ash, slag and natural pozzolan, which need no new kilns.</t>
-  </si>
-  <si>
-    <t>What the model still leaves out</t>
-  </si>
-  <si>
-    <t>The purchase cost of slag, fly ash and raw clay, and the non-energy costs of the clinker that substitution avoids (raw meal, kiln maintenance, labor) are both left out. For calcined clay the cost studies find the avoided clinker costs larger than the clay (LC3 cash costs 6-33 percent below ordinary cement), so leaving both out errs against blending. For slag and fly ash, which sell for about $40-140 a tonne in the U.S. (USGS), the purchase cost can exceed the clinker they replace, so leaving it out errs the other way. The two roughly offset for the marginal mix used here.</t>
+    <t>About $150 per tonne of annual calcined-clay capacity in 2024 dollars ($110 in 2012 dollars), covering the calciner, dryer, cooler and storage but not extra cement grinding: the middle of plants built or announced since 2020 ($100-290 per tonne; the 14 disclosed projects average about $123). No U.S. plant cost has been published, so the range is wide: use about $90 for a retrofit at an integrated plant and about $300 for a small or greenfield plant.</t>
+  </si>
+  <si>
+    <t>Related costs</t>
+  </si>
+  <si>
+    <t>The heat to make calcined clay and the other materials, and the net cost of buying them less the non-fuel costs of the clinker they replace, are in the CSMI file (Cement Substitute Material Inputs).</t>
   </si>
   <si>
     <t>Confidence</t>
@@ -195,12 +195,6 @@
     <t>Derivation tab</t>
   </si>
   <si>
-    <t>Calcined clay share of clinker substitution (dimensionless)</t>
-  </si>
-  <si>
-    <t>Same marginal mix as SCMEI: 50 percent calcined clay</t>
-  </si>
-  <si>
     <t>Live checks</t>
   </si>
   <si>
@@ -213,16 +207,10 @@
     <t>Capital cost positive and below 500 2012-$ per t (count failing)</t>
   </si>
   <si>
-    <t>Share between 0 and 1 (count failing)</t>
-  </si>
-  <si>
     <t>Unit: see rows</t>
   </si>
   <si>
     <t>Calcined Clay Plant Capital Cost (2012 USD per metric ton of annual capacity)</t>
-  </si>
-  <si>
-    <t>Calcined Clay Share of Clinker Substitution (dimensionless)</t>
   </si>
 </sst>
 </file>
@@ -785,7 +773,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>30</v>
       </c>
@@ -793,7 +781,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>32</v>
       </c>
@@ -899,7 +887,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -935,17 +923,6 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5">
-        <v>0.5</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -953,7 +930,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -961,23 +938,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <f>COUNTIF(CSCC!B2,"&lt;=0")+COUNTIF(CSCC!B2,"&gt;500")</f>
@@ -985,19 +962,6 @@
       </c>
       <c r="C3" t="str">
         <f>IF(B3=0,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4">
-        <f>COUNTIF(CSCC!B3,"&lt;0")+COUNTIF(CSCC!B3,"&gt;1")</f>
-        <v>0</v>
-      </c>
-      <c r="C4" t="str">
-        <f>IF(B4=0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -1011,7 +975,7 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
@@ -1019,7 +983,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B1" t="s">
         <v>38</v>
@@ -1027,20 +991,11 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B2">
         <f>Assumptions!B4</f>
         <v>109.78740089706683</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3">
-        <f>Assumptions!B5</f>
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
